--- a/datasets/TanyaParlimen_QnA.xlsx
+++ b/datasets/TanyaParlimen_QnA.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="1681" documentId="11_E60897F41BE170836B02CE998F75CCDC64E183C8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66F5590-9E8C-40AF-A281-A6E01094C95D}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AimanFaris\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B93D67A5-D4FB-4971-B434-C27154CAEE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="945">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="943">
   <si>
     <t>No</t>
   </si>
@@ -1866,9 +1871,6 @@
     <t>Kerajaan Persekutuan telah memperuntukkan sebanyak RM103.5 juta bagi tahun 2025 dan meningkat kepada RM143 juta pada tahun 2026 khusus bagi pelaksanaan projek-projek bekalan air luar bandar di seluruh negeri Sabah.</t>
   </si>
   <si>
-    <t>kr_2026-7-14, ms 9</t>
-  </si>
-  <si>
     <t>Berapakah anggaran keseluruhan bantuan sosial tunai STR dan SARA yang disalurkan kepada penerima di Sabah?</t>
   </si>
   <si>
@@ -1981,9 +1983,6 @@
   </si>
   <si>
     <t>Projek menaik taraf sumber air mentah dan loji rawatan air dilaksanakan oleh kontraktor West Sdn Bhd dengan kapasiti 5 juta liter sehari (MLD), di mana tarikh siap asal pada 12 Mei 2026 telah diberikan Lanjutan Masa (EOT) sehingga 10 Disember 2027.</t>
-  </si>
-  <si>
-    <t>kr_2026-7-15, ms 5</t>
   </si>
   <si>
     <t>Apakah projek pembangunan pendidikan yang sedang dinaik taraf di Gugusan Umas di bawah Unit Penyelarasan Pelaksanaan (ICU)?</t>
@@ -2926,7 +2925,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2976,7 +2975,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2986,6 +2985,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3054,7 +3059,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3101,6 +3106,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3119,9 +3128,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3159,7 +3168,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3265,7 +3274,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3407,7 +3416,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3443,16 +3452,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I374"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.140625" customWidth="1"/>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
     <col min="2" max="2" width="152" customWidth="1"/>
-    <col min="3" max="3" width="147.5703125" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="5" max="5" width="26.42578125" customWidth="1"/>
+    <col min="3" max="3" width="147.54296875" customWidth="1"/>
+    <col min="4" max="4" width="26.81640625" customWidth="1"/>
+    <col min="5" max="5" width="26.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="29.25" customHeight="1">
+    <row r="1" spans="1:5" ht="29.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3469,7 +3478,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" s="8">
         <v>1</v>
       </c>
@@ -3486,7 +3495,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -3503,7 +3512,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" s="8">
         <v>3</v>
       </c>
@@ -3520,7 +3529,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="45.75">
+    <row r="5" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A5" s="8">
         <v>4</v>
       </c>
@@ -3537,7 +3546,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30.75">
+    <row r="6" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="8">
         <v>5</v>
       </c>
@@ -3554,7 +3563,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" s="8">
         <v>6</v>
       </c>
@@ -3571,7 +3580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30.75">
+    <row r="8" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="8">
         <v>7</v>
       </c>
@@ -3588,7 +3597,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="30.75">
+    <row r="9" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" s="8">
         <v>8</v>
       </c>
@@ -3605,7 +3614,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" s="8">
         <v>9</v>
       </c>
@@ -3622,7 +3631,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="45.75">
+    <row r="11" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A11" s="8">
         <v>10</v>
       </c>
@@ -3639,7 +3648,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="45.75">
+    <row r="12" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="8">
         <v>11</v>
       </c>
@@ -3656,7 +3665,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30.75">
+    <row r="13" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="8">
         <v>12</v>
       </c>
@@ -3673,7 +3682,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="45.75">
+    <row r="14" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="8">
         <v>13</v>
       </c>
@@ -3690,7 +3699,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30.75">
+    <row r="15" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="8">
         <v>14</v>
       </c>
@@ -3707,7 +3716,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="30.75">
+    <row r="16" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="8">
         <v>15</v>
       </c>
@@ -3724,7 +3733,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="45.75">
+    <row r="17" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="8">
         <v>16</v>
       </c>
@@ -3741,7 +3750,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="45.75">
+    <row r="18" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="8">
         <v>17</v>
       </c>
@@ -3758,7 +3767,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="30.75">
+    <row r="19" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="8">
         <v>18</v>
       </c>
@@ -3775,7 +3784,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="30.75">
+    <row r="20" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="8">
         <v>19</v>
       </c>
@@ -3792,7 +3801,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="45.75">
+    <row r="21" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -3809,7 +3818,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="45.75">
+    <row r="22" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A22" s="8">
         <v>21</v>
       </c>
@@ -3826,7 +3835,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="30.75">
+    <row r="23" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="8">
         <v>22</v>
       </c>
@@ -3843,7 +3852,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="8">
         <v>23</v>
       </c>
@@ -3860,7 +3869,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="30.75">
+    <row r="25" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A25" s="8">
         <v>24</v>
       </c>
@@ -3877,7 +3886,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="30.75">
+    <row r="26" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A26" s="8">
         <v>25</v>
       </c>
@@ -3894,7 +3903,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="45.75">
+    <row r="27" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="8">
         <v>26</v>
       </c>
@@ -3911,7 +3920,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="30.75">
+    <row r="28" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="8">
         <v>27</v>
       </c>
@@ -3928,7 +3937,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="45.75">
+    <row r="29" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A29" s="8">
         <v>28</v>
       </c>
@@ -3945,7 +3954,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="8">
         <v>29</v>
       </c>
@@ -3962,7 +3971,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="8">
         <v>30</v>
       </c>
@@ -3979,7 +3988,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" s="8">
         <v>31</v>
       </c>
@@ -3996,7 +4005,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="33" spans="1:5" ht="30.75">
+    <row r="33" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="8">
         <v>32</v>
       </c>
@@ -4013,7 +4022,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" s="8">
         <v>33</v>
       </c>
@@ -4030,7 +4039,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="35" spans="1:5" ht="30.75">
+    <row r="35" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A35" s="8">
         <v>34</v>
       </c>
@@ -4047,7 +4056,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="36" spans="1:5" ht="30.75">
+    <row r="36" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A36" s="8">
         <v>35</v>
       </c>
@@ -4064,7 +4073,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="106.5">
+    <row r="37" spans="1:5" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A37" s="8">
         <v>36</v>
       </c>
@@ -4081,7 +4090,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" s="8">
         <v>37</v>
       </c>
@@ -4098,7 +4107,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="30.75">
+    <row r="39" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A39" s="8">
         <v>38</v>
       </c>
@@ -4115,7 +4124,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="40" spans="1:5" ht="30.75">
+    <row r="40" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A40" s="8">
         <v>39</v>
       </c>
@@ -4132,7 +4141,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="41" spans="1:5" ht="30.75">
+    <row r="41" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A41" s="8">
         <v>40</v>
       </c>
@@ -4149,7 +4158,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="30.75">
+    <row r="42" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A42" s="8">
         <v>41</v>
       </c>
@@ -4166,7 +4175,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="43" spans="1:5" ht="45.75">
+    <row r="43" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A43" s="8">
         <v>42</v>
       </c>
@@ -4183,7 +4192,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="30.75">
+    <row r="44" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A44" s="8">
         <v>43</v>
       </c>
@@ -4200,7 +4209,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" s="8">
         <v>44</v>
       </c>
@@ -4217,7 +4226,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="30.75">
+    <row r="46" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A46" s="8">
         <v>45</v>
       </c>
@@ -4234,7 +4243,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" s="8">
         <v>46</v>
       </c>
@@ -4251,7 +4260,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" s="8">
         <v>47</v>
       </c>
@@ -4268,7 +4277,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="30.75">
+    <row r="49" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A49" s="8">
         <v>48</v>
       </c>
@@ -4285,7 +4294,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="91.5">
+    <row r="50" spans="1:5" ht="87" x14ac:dyDescent="0.35">
       <c r="A50" s="8">
         <v>49</v>
       </c>
@@ -4302,7 +4311,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="30.75">
+    <row r="51" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A51" s="8">
         <v>50</v>
       </c>
@@ -4319,7 +4328,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="30.75">
+    <row r="52" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A52" s="8">
         <v>51</v>
       </c>
@@ -4336,7 +4345,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="45.75">
+    <row r="53" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="8">
         <v>52</v>
       </c>
@@ -4353,7 +4362,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="54" spans="1:5" ht="45.75">
+    <row r="54" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="8">
         <v>53</v>
       </c>
@@ -4370,7 +4379,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="45.75">
+    <row r="55" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A55" s="8">
         <v>54</v>
       </c>
@@ -4387,7 +4396,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="30.75">
+    <row r="56" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A56" s="8">
         <v>55</v>
       </c>
@@ -4404,7 +4413,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="30.75">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" s="8">
         <v>56</v>
       </c>
@@ -4421,7 +4430,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="58" spans="1:5" ht="45.75">
+    <row r="58" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A58" s="8">
         <v>57</v>
       </c>
@@ -4438,7 +4447,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="59" spans="1:5" ht="30.75">
+    <row r="59" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A59" s="8">
         <v>58</v>
       </c>
@@ -4455,7 +4464,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="60" spans="1:5" ht="30.75">
+    <row r="60" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A60" s="8">
         <v>59</v>
       </c>
@@ -4472,7 +4481,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="30.75">
+    <row r="61" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A61" s="8">
         <v>60</v>
       </c>
@@ -4489,7 +4498,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="30.75">
+    <row r="62" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A62" s="8">
         <v>61</v>
       </c>
@@ -4506,7 +4515,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="45.75">
+    <row r="63" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A63" s="8">
         <v>62</v>
       </c>
@@ -4523,7 +4532,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:5" ht="30.75">
+    <row r="64" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A64" s="8">
         <v>63</v>
       </c>
@@ -4540,7 +4549,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:5" ht="30.75">
+    <row r="65" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A65" s="8">
         <v>64</v>
       </c>
@@ -4557,7 +4566,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" s="8">
         <v>65</v>
       </c>
@@ -4574,7 +4583,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:5" ht="30.75">
+    <row r="67" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A67" s="8">
         <v>66</v>
       </c>
@@ -4591,7 +4600,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" s="8">
         <v>67</v>
       </c>
@@ -4608,7 +4617,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="69" spans="1:5" ht="45.75">
+    <row r="69" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A69" s="8">
         <v>68</v>
       </c>
@@ -4625,7 +4634,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="70" spans="1:5" ht="30.75">
+    <row r="70" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A70" s="8">
         <v>69</v>
       </c>
@@ -4642,7 +4651,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:5" ht="30.75">
+    <row r="71" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A71" s="8">
         <v>70</v>
       </c>
@@ -4659,7 +4668,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="72" spans="1:5" ht="45.75">
+    <row r="72" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A72" s="8">
         <v>71</v>
       </c>
@@ -4676,7 +4685,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" s="8">
         <v>72</v>
       </c>
@@ -4693,7 +4702,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="30.75">
+    <row r="74" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A74" s="8">
         <v>73</v>
       </c>
@@ -4710,7 +4719,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="30.75">
+    <row r="75" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A75" s="8">
         <v>74</v>
       </c>
@@ -4727,7 +4736,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="30.75">
+    <row r="76" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A76" s="8">
         <v>75</v>
       </c>
@@ -4744,7 +4753,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="30.75">
+    <row r="77" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A77" s="8">
         <v>76</v>
       </c>
@@ -4761,7 +4770,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="45.75">
+    <row r="78" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A78" s="8">
         <v>77</v>
       </c>
@@ -4778,7 +4787,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="8">
         <v>78</v>
       </c>
@@ -4795,7 +4804,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="8">
         <v>79</v>
       </c>
@@ -4812,7 +4821,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" s="8">
         <v>80</v>
       </c>
@@ -4829,7 +4838,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" s="8">
         <v>81</v>
       </c>
@@ -4846,7 +4855,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="30.75">
+    <row r="83" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A83" s="8">
         <v>82</v>
       </c>
@@ -4863,7 +4872,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" s="8">
         <v>83</v>
       </c>
@@ -4880,7 +4889,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="85" spans="1:5" ht="45.75">
+    <row r="85" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A85" s="8">
         <v>84</v>
       </c>
@@ -4897,7 +4906,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="86" spans="1:5" ht="30.75">
+    <row r="86" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A86" s="8">
         <v>85</v>
       </c>
@@ -4914,7 +4923,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="30.75">
+    <row r="87" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A87" s="8">
         <v>86</v>
       </c>
@@ -4931,7 +4940,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="30.75">
+    <row r="88" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A88" s="8">
         <v>87</v>
       </c>
@@ -4948,7 +4957,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="45.75">
+    <row r="89" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A89" s="8">
         <v>88</v>
       </c>
@@ -4965,7 +4974,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="90" spans="1:5" ht="30.75">
+    <row r="90" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A90" s="8">
         <v>89</v>
       </c>
@@ -4982,7 +4991,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="91" spans="1:5" ht="45.75">
+    <row r="91" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A91" s="8">
         <v>90</v>
       </c>
@@ -4999,7 +5008,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="92" spans="1:5" ht="30.75">
+    <row r="92" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A92" s="8">
         <v>91</v>
       </c>
@@ -5016,7 +5025,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="8">
         <v>92</v>
       </c>
@@ -5033,7 +5042,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="94" spans="1:5" ht="30.75">
+    <row r="94" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A94" s="8">
         <v>93</v>
       </c>
@@ -5050,7 +5059,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" s="8">
         <v>94</v>
       </c>
@@ -5067,7 +5076,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="30.75">
+    <row r="96" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A96" s="8">
         <v>95</v>
       </c>
@@ -5084,7 +5093,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="45.75">
+    <row r="97" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A97" s="8">
         <v>96</v>
       </c>
@@ -5101,7 +5110,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="45.75">
+    <row r="98" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A98" s="8">
         <v>97</v>
       </c>
@@ -5118,7 +5127,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" s="8">
         <v>98</v>
       </c>
@@ -5135,7 +5144,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="45.75">
+    <row r="100" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A100" s="8">
         <v>99</v>
       </c>
@@ -5152,7 +5161,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" s="8">
         <v>100</v>
       </c>
@@ -5167,7 +5176,7 @@
       </c>
       <c r="E101" s="8"/>
     </row>
-    <row r="102" spans="1:5" ht="30.75">
+    <row r="102" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A102" s="6">
         <v>101</v>
       </c>
@@ -5184,7 +5193,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" s="7">
         <v>102</v>
       </c>
@@ -5201,7 +5210,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="30.75">
+    <row r="104" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A104" s="7">
         <v>103</v>
       </c>
@@ -5218,7 +5227,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="30.75">
+    <row r="105" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A105" s="7">
         <v>104</v>
       </c>
@@ -5235,7 +5244,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="106" spans="1:5" ht="30.75">
+    <row r="106" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A106" s="7">
         <v>105</v>
       </c>
@@ -5252,7 +5261,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="45.75">
+    <row r="107" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A107" s="7">
         <v>106</v>
       </c>
@@ -5269,7 +5278,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="108" spans="1:5" ht="30.75">
+    <row r="108" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A108" s="7">
         <v>107</v>
       </c>
@@ -5286,7 +5295,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="109" spans="1:5" ht="30.75">
+    <row r="109" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A109" s="7">
         <v>108</v>
       </c>
@@ -5303,7 +5312,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="110" spans="1:5" ht="30.75">
+    <row r="110" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A110" s="7">
         <v>109</v>
       </c>
@@ -5320,7 +5329,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="111" spans="1:5" ht="45.75">
+    <row r="111" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A111" s="7">
         <v>110</v>
       </c>
@@ -5337,7 +5346,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="112" spans="1:5" ht="30.75">
+    <row r="112" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A112" s="7">
         <v>111</v>
       </c>
@@ -5354,7 +5363,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="113" spans="1:5" ht="45.75">
+    <row r="113" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A113" s="7">
         <v>112</v>
       </c>
@@ -5371,7 +5380,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="114" spans="1:5" ht="30.75">
+    <row r="114" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A114" s="7">
         <v>113</v>
       </c>
@@ -5388,7 +5397,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="115" spans="1:5" ht="30.75">
+    <row r="115" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A115" s="7">
         <v>114</v>
       </c>
@@ -5405,7 +5414,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="116" spans="1:5" ht="45.75">
+    <row r="116" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A116" s="7">
         <v>115</v>
       </c>
@@ -5422,7 +5431,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="30.75">
+    <row r="117" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A117" s="6">
         <v>116</v>
       </c>
@@ -5439,7 +5448,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="30.75">
+    <row r="118" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A118" s="7">
         <v>117</v>
       </c>
@@ -5456,7 +5465,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="45.75">
+    <row r="119" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A119" s="7">
         <v>118</v>
       </c>
@@ -5473,7 +5482,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="30.75">
+    <row r="120" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A120" s="7">
         <v>119</v>
       </c>
@@ -5490,7 +5499,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="121" spans="1:5" ht="30.75">
+    <row r="121" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A121" s="7">
         <v>120</v>
       </c>
@@ -5507,7 +5516,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="122" spans="1:5" ht="45.75">
+    <row r="122" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A122" s="7">
         <v>121</v>
       </c>
@@ -5524,7 +5533,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="123" spans="1:5" ht="45.75">
+    <row r="123" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A123" s="7">
         <v>122</v>
       </c>
@@ -5541,7 +5550,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="30.75">
+    <row r="124" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A124" s="7">
         <v>123</v>
       </c>
@@ -5558,7 +5567,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="30.75">
+    <row r="125" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A125" s="7">
         <v>124</v>
       </c>
@@ -5575,7 +5584,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="45.75">
+    <row r="126" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A126" s="7">
         <v>125</v>
       </c>
@@ -5592,7 +5601,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="127" spans="1:5" ht="30.75">
+    <row r="127" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A127" s="7">
         <v>126</v>
       </c>
@@ -5609,7 +5618,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="128" spans="1:5" ht="45.75">
+    <row r="128" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A128" s="7">
         <v>127</v>
       </c>
@@ -5626,7 +5635,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="30.75">
+    <row r="129" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A129" s="7">
         <v>128</v>
       </c>
@@ -5643,7 +5652,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="45.75">
+    <row r="130" spans="1:9" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A130" s="7">
         <v>129</v>
       </c>
@@ -5660,7 +5669,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="30.75">
+    <row r="131" spans="1:9" ht="29" x14ac:dyDescent="0.35">
       <c r="A131" s="7">
         <v>130</v>
       </c>
@@ -5677,7 +5686,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="132" spans="1:9">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A132" s="16">
         <v>131</v>
       </c>
@@ -5694,7 +5703,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="133" spans="1:9">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A133" s="16">
         <v>132</v>
       </c>
@@ -5711,7 +5720,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="134" spans="1:9">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A134" s="16">
         <v>133</v>
       </c>
@@ -5728,7 +5737,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="135" spans="1:9">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A135" s="16">
         <v>134</v>
       </c>
@@ -5745,7 +5754,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="136" spans="1:9">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A136" s="16">
         <v>135</v>
       </c>
@@ -5762,7 +5771,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="137" spans="1:9">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A137" s="16">
         <v>136</v>
       </c>
@@ -5779,7 +5788,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="138" spans="1:9">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A138" s="16">
         <v>137</v>
       </c>
@@ -5796,7 +5805,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="139" spans="1:9">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A139" s="16">
         <v>138</v>
       </c>
@@ -5813,7 +5822,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="140" spans="1:9">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A140" s="6">
         <v>139</v>
       </c>
@@ -5834,7 +5843,7 @@
       <c r="H140" s="17"/>
       <c r="I140" s="17"/>
     </row>
-    <row r="141" spans="1:9">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A141" s="7">
         <v>140</v>
       </c>
@@ -5855,7 +5864,7 @@
       <c r="H141" s="17"/>
       <c r="I141" s="17"/>
     </row>
-    <row r="142" spans="1:9">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A142" s="7">
         <v>141</v>
       </c>
@@ -5876,7 +5885,7 @@
       <c r="H142" s="17"/>
       <c r="I142" s="17"/>
     </row>
-    <row r="143" spans="1:9">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A143" s="7">
         <v>142</v>
       </c>
@@ -5897,7 +5906,7 @@
       <c r="H143" s="17"/>
       <c r="I143" s="17"/>
     </row>
-    <row r="144" spans="1:9">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A144" s="7">
         <v>143</v>
       </c>
@@ -5918,7 +5927,7 @@
       <c r="H144" s="17"/>
       <c r="I144" s="17"/>
     </row>
-    <row r="145" spans="1:9">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A145" s="7">
         <v>144</v>
       </c>
@@ -5939,7 +5948,7 @@
       <c r="H145" s="17"/>
       <c r="I145" s="17"/>
     </row>
-    <row r="146" spans="1:9">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A146" s="7">
         <v>145</v>
       </c>
@@ -5960,7 +5969,7 @@
       <c r="H146" s="17"/>
       <c r="I146" s="17"/>
     </row>
-    <row r="147" spans="1:9">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A147" s="7">
         <v>146</v>
       </c>
@@ -5981,7 +5990,7 @@
       <c r="H147" s="17"/>
       <c r="I147" s="17"/>
     </row>
-    <row r="148" spans="1:9">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A148" s="7">
         <v>147</v>
       </c>
@@ -6002,7 +6011,7 @@
       <c r="H148" s="17"/>
       <c r="I148" s="17"/>
     </row>
-    <row r="149" spans="1:9">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A149" s="7">
         <v>148</v>
       </c>
@@ -6023,7 +6032,7 @@
       <c r="H149" s="17"/>
       <c r="I149" s="17"/>
     </row>
-    <row r="150" spans="1:9">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A150" s="7">
         <v>149</v>
       </c>
@@ -6044,7 +6053,7 @@
       <c r="H150" s="17"/>
       <c r="I150" s="17"/>
     </row>
-    <row r="151" spans="1:9">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A151" s="7">
         <v>150</v>
       </c>
@@ -6065,7 +6074,7 @@
       <c r="H151" s="17"/>
       <c r="I151" s="17"/>
     </row>
-    <row r="152" spans="1:9">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A152" s="7">
         <v>151</v>
       </c>
@@ -6086,7 +6095,7 @@
       <c r="H152" s="17"/>
       <c r="I152" s="17"/>
     </row>
-    <row r="153" spans="1:9">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A153" s="6">
         <v>152</v>
       </c>
@@ -6104,7 +6113,7 @@
       </c>
       <c r="F153" s="17"/>
     </row>
-    <row r="154" spans="1:9">
+    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A154" s="7">
         <v>153</v>
       </c>
@@ -6122,7 +6131,7 @@
       </c>
       <c r="F154" s="17"/>
     </row>
-    <row r="155" spans="1:9">
+    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A155" s="7">
         <v>154</v>
       </c>
@@ -6140,7 +6149,7 @@
       </c>
       <c r="F155" s="17"/>
     </row>
-    <row r="156" spans="1:9">
+    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A156" s="7">
         <v>155</v>
       </c>
@@ -6158,7 +6167,7 @@
       </c>
       <c r="F156" s="17"/>
     </row>
-    <row r="157" spans="1:9">
+    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A157" s="7">
         <v>156</v>
       </c>
@@ -6176,7 +6185,7 @@
       </c>
       <c r="F157" s="17"/>
     </row>
-    <row r="158" spans="1:9">
+    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A158" s="7">
         <v>157</v>
       </c>
@@ -6194,7 +6203,7 @@
       </c>
       <c r="F158" s="17"/>
     </row>
-    <row r="159" spans="1:9">
+    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A159" s="7">
         <v>158</v>
       </c>
@@ -6212,7 +6221,7 @@
       </c>
       <c r="F159" s="17"/>
     </row>
-    <row r="160" spans="1:9">
+    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A160" s="7">
         <v>159</v>
       </c>
@@ -6230,7 +6239,7 @@
       </c>
       <c r="F160" s="17"/>
     </row>
-    <row r="161" spans="1:6">
+    <row r="161" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A161" s="7">
         <v>160</v>
       </c>
@@ -6248,7 +6257,7 @@
       </c>
       <c r="F161" s="17"/>
     </row>
-    <row r="162" spans="1:6">
+    <row r="162" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A162" s="7">
         <v>161</v>
       </c>
@@ -6266,7 +6275,7 @@
       </c>
       <c r="F162" s="17"/>
     </row>
-    <row r="163" spans="1:6">
+    <row r="163" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A163" s="7">
         <v>162</v>
       </c>
@@ -6284,7 +6293,7 @@
       </c>
       <c r="F163" s="17"/>
     </row>
-    <row r="164" spans="1:6" ht="30.75">
+    <row r="164" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A164" s="7">
         <v>163</v>
       </c>
@@ -6302,7 +6311,7 @@
       </c>
       <c r="F164" s="17"/>
     </row>
-    <row r="165" spans="1:6">
+    <row r="165" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A165" s="7">
         <v>164</v>
       </c>
@@ -6320,7 +6329,7 @@
       </c>
       <c r="F165" s="17"/>
     </row>
-    <row r="166" spans="1:6">
+    <row r="166" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A166" s="7">
         <v>165</v>
       </c>
@@ -6338,7 +6347,7 @@
       </c>
       <c r="F166" s="17"/>
     </row>
-    <row r="167" spans="1:6">
+    <row r="167" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A167" s="7">
         <v>166</v>
       </c>
@@ -6356,7 +6365,7 @@
       </c>
       <c r="F167" s="17"/>
     </row>
-    <row r="168" spans="1:6">
+    <row r="168" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A168" s="7">
         <v>167</v>
       </c>
@@ -6374,7 +6383,7 @@
       </c>
       <c r="F168" s="17"/>
     </row>
-    <row r="169" spans="1:6">
+    <row r="169" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A169" s="6">
         <v>168</v>
       </c>
@@ -6392,7 +6401,7 @@
       </c>
       <c r="F169" s="17"/>
     </row>
-    <row r="170" spans="1:6">
+    <row r="170" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A170" s="7">
         <v>169</v>
       </c>
@@ -6410,7 +6419,7 @@
       </c>
       <c r="F170" s="17"/>
     </row>
-    <row r="171" spans="1:6">
+    <row r="171" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A171" s="7">
         <v>170</v>
       </c>
@@ -6428,7 +6437,7 @@
       </c>
       <c r="F171" s="17"/>
     </row>
-    <row r="172" spans="1:6">
+    <row r="172" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A172" s="7">
         <v>171</v>
       </c>
@@ -6446,7 +6455,7 @@
       </c>
       <c r="F172" s="17"/>
     </row>
-    <row r="173" spans="1:6">
+    <row r="173" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A173" s="7">
         <v>172</v>
       </c>
@@ -6464,7 +6473,7 @@
       </c>
       <c r="F173" s="17"/>
     </row>
-    <row r="174" spans="1:6">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A174" s="7">
         <v>173</v>
       </c>
@@ -6482,7 +6491,7 @@
       </c>
       <c r="F174" s="17"/>
     </row>
-    <row r="175" spans="1:6">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A175" s="7">
         <v>174</v>
       </c>
@@ -6500,7 +6509,7 @@
       </c>
       <c r="F175" s="17"/>
     </row>
-    <row r="176" spans="1:6">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A176" s="7">
         <v>175</v>
       </c>
@@ -6518,7 +6527,7 @@
       </c>
       <c r="F176" s="17"/>
     </row>
-    <row r="177" spans="1:6">
+    <row r="177" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A177" s="7">
         <v>176</v>
       </c>
@@ -6536,7 +6545,7 @@
       </c>
       <c r="F177" s="17"/>
     </row>
-    <row r="178" spans="1:6">
+    <row r="178" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A178" s="7">
         <v>177</v>
       </c>
@@ -6554,7 +6563,7 @@
       </c>
       <c r="F178" s="17"/>
     </row>
-    <row r="179" spans="1:6">
+    <row r="179" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A179" s="7">
         <v>178</v>
       </c>
@@ -6572,7 +6581,7 @@
       </c>
       <c r="F179" s="17"/>
     </row>
-    <row r="180" spans="1:6">
+    <row r="180" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A180" s="7">
         <v>179</v>
       </c>
@@ -6590,7 +6599,7 @@
       </c>
       <c r="F180" s="17"/>
     </row>
-    <row r="181" spans="1:6">
+    <row r="181" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A181" s="7">
         <v>180</v>
       </c>
@@ -6608,7 +6617,7 @@
       </c>
       <c r="F181" s="17"/>
     </row>
-    <row r="182" spans="1:6">
+    <row r="182" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A182" s="7">
         <v>181</v>
       </c>
@@ -6626,7 +6635,7 @@
       </c>
       <c r="F182" s="17"/>
     </row>
-    <row r="183" spans="1:6">
+    <row r="183" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A183" s="7">
         <v>182</v>
       </c>
@@ -6644,7 +6653,7 @@
       </c>
       <c r="F183" s="17"/>
     </row>
-    <row r="184" spans="1:6">
+    <row r="184" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A184" s="7">
         <v>183</v>
       </c>
@@ -6662,7 +6671,7 @@
       </c>
       <c r="F184" s="17"/>
     </row>
-    <row r="185" spans="1:6">
+    <row r="185" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A185" s="7">
         <v>184</v>
       </c>
@@ -6680,7 +6689,7 @@
       </c>
       <c r="F185" s="17"/>
     </row>
-    <row r="186" spans="1:6">
+    <row r="186" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A186" s="7">
         <v>185</v>
       </c>
@@ -6698,7 +6707,7 @@
       </c>
       <c r="F186" s="17"/>
     </row>
-    <row r="187" spans="1:6">
+    <row r="187" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A187" s="7">
         <v>186</v>
       </c>
@@ -6716,7 +6725,7 @@
       </c>
       <c r="F187" s="17"/>
     </row>
-    <row r="188" spans="1:6">
+    <row r="188" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A188" s="7">
         <v>187</v>
       </c>
@@ -6734,7 +6743,7 @@
       </c>
       <c r="F188" s="17"/>
     </row>
-    <row r="189" spans="1:6">
+    <row r="189" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A189" s="7">
         <v>188</v>
       </c>
@@ -6752,7 +6761,7 @@
       </c>
       <c r="F189" s="17"/>
     </row>
-    <row r="190" spans="1:6">
+    <row r="190" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A190" s="7">
         <v>189</v>
       </c>
@@ -6770,7 +6779,7 @@
       </c>
       <c r="F190" s="17"/>
     </row>
-    <row r="191" spans="1:6">
+    <row r="191" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A191" s="7">
         <v>190</v>
       </c>
@@ -6788,7 +6797,7 @@
       </c>
       <c r="F191" s="17"/>
     </row>
-    <row r="192" spans="1:6">
+    <row r="192" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A192" s="7">
         <v>191</v>
       </c>
@@ -6806,7 +6815,7 @@
       </c>
       <c r="F192" s="17"/>
     </row>
-    <row r="193" spans="1:6">
+    <row r="193" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A193" s="7">
         <v>192</v>
       </c>
@@ -6824,7 +6833,7 @@
       </c>
       <c r="F193" s="17"/>
     </row>
-    <row r="194" spans="1:6">
+    <row r="194" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A194" s="7">
         <v>193</v>
       </c>
@@ -6842,7 +6851,7 @@
       </c>
       <c r="F194" s="17"/>
     </row>
-    <row r="195" spans="1:6">
+    <row r="195" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A195" s="7">
         <v>194</v>
       </c>
@@ -6860,7 +6869,7 @@
       </c>
       <c r="F195" s="17"/>
     </row>
-    <row r="196" spans="1:6">
+    <row r="196" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A196" s="7">
         <v>195</v>
       </c>
@@ -6878,7 +6887,7 @@
       </c>
       <c r="F196" s="17"/>
     </row>
-    <row r="197" spans="1:6">
+    <row r="197" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A197" s="7">
         <v>196</v>
       </c>
@@ -6896,7 +6905,7 @@
       </c>
       <c r="F197" s="17"/>
     </row>
-    <row r="198" spans="1:6">
+    <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" s="7">
         <v>197</v>
       </c>
@@ -6914,7 +6923,7 @@
       </c>
       <c r="F198" s="17"/>
     </row>
-    <row r="199" spans="1:6">
+    <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" s="7">
         <v>198</v>
       </c>
@@ -6932,7 +6941,7 @@
       </c>
       <c r="F199" s="17"/>
     </row>
-    <row r="200" spans="1:6">
+    <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" s="7">
         <v>199</v>
       </c>
@@ -6950,7 +6959,7 @@
       </c>
       <c r="F200" s="17"/>
     </row>
-    <row r="201" spans="1:6">
+    <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" s="8">
         <v>200</v>
       </c>
@@ -6967,7 +6976,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="202" spans="1:6" ht="45.75">
+    <row r="202" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A202" s="16" cm="1">
         <f t="array" ref="A202:A302">_xlfn.SEQUENCE(101,,200)</f>
         <v>200</v>
@@ -6985,7 +6994,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="203" spans="1:6" ht="30.75">
+    <row r="203" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A203" s="16">
         <v>201</v>
       </c>
@@ -7002,7 +7011,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="204" spans="1:6" ht="30.75">
+    <row r="204" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A204" s="16">
         <v>202</v>
       </c>
@@ -7019,7 +7028,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="205" spans="1:6" ht="30.75">
+    <row r="205" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A205" s="8">
         <v>203</v>
       </c>
@@ -7036,7 +7045,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="206" spans="1:6" ht="45.75">
+    <row r="206" spans="1:6" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A206" s="8">
         <v>204</v>
       </c>
@@ -7053,7 +7062,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="207" spans="1:6" ht="30.75">
+    <row r="207" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A207" s="8">
         <v>205</v>
       </c>
@@ -7070,7 +7079,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="208" spans="1:6" ht="30.75">
+    <row r="208" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A208" s="8">
         <v>206</v>
       </c>
@@ -7087,7 +7096,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="209" spans="1:5" ht="30.75">
+    <row r="209" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A209" s="8">
         <v>207</v>
       </c>
@@ -7104,7 +7113,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="210" spans="1:5" ht="30.75">
+    <row r="210" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="8">
         <v>208</v>
       </c>
@@ -7121,7 +7130,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="211" spans="1:5" ht="30.75">
+    <row r="211" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A211" s="8">
         <v>209</v>
       </c>
@@ -7138,7 +7147,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="212" spans="1:5" ht="45.75">
+    <row r="212" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A212" s="8">
         <v>210</v>
       </c>
@@ -7155,7 +7164,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="213" spans="1:5" ht="30.75">
+    <row r="213" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A213" s="8">
         <v>211</v>
       </c>
@@ -7172,7 +7181,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="214" spans="1:5" ht="30.75">
+    <row r="214" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A214" s="8">
         <v>212</v>
       </c>
@@ -7189,7 +7198,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="215" spans="1:5" ht="30.75">
+    <row r="215" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A215" s="8">
         <v>213</v>
       </c>
@@ -7206,7 +7215,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="216" spans="1:5" ht="30.75">
+    <row r="216" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A216" s="8">
         <v>214</v>
       </c>
@@ -7223,7 +7232,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="217" spans="1:5" ht="30.75">
+    <row r="217" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A217" s="8">
         <v>215</v>
       </c>
@@ -7240,7 +7249,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="218" spans="1:5" ht="30.75">
+    <row r="218" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A218" s="8">
         <v>216</v>
       </c>
@@ -7257,7 +7266,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="219" spans="1:5" ht="45.75">
+    <row r="219" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A219" s="8">
         <v>217</v>
       </c>
@@ -7274,7 +7283,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="220" spans="1:5" ht="30.75">
+    <row r="220" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A220" s="8">
         <v>218</v>
       </c>
@@ -7291,7 +7300,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="221" spans="1:5" ht="30.75">
+    <row r="221" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A221" s="8">
         <v>219</v>
       </c>
@@ -7308,7 +7317,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="222" spans="1:5" ht="30.75">
+    <row r="222" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A222" s="8">
         <v>220</v>
       </c>
@@ -7325,7 +7334,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="223" spans="1:5" ht="30.75">
+    <row r="223" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A223" s="8">
         <v>221</v>
       </c>
@@ -7342,7 +7351,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="224" spans="1:5" ht="30.75">
+    <row r="224" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A224" s="8">
         <v>222</v>
       </c>
@@ -7359,7 +7368,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="225" spans="1:5" ht="45.75">
+    <row r="225" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A225" s="8">
         <v>223</v>
       </c>
@@ -7376,7 +7385,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="226" spans="1:5" ht="45.75">
+    <row r="226" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A226" s="8">
         <v>224</v>
       </c>
@@ -7393,7 +7402,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="227" spans="1:5" ht="45.75">
+    <row r="227" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A227" s="8">
         <v>225</v>
       </c>
@@ -7410,7 +7419,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A228" s="8">
         <v>226</v>
       </c>
@@ -7427,7 +7436,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="229" spans="1:5" ht="30.75">
+    <row r="229" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A229" s="8">
         <v>227</v>
       </c>
@@ -7444,7 +7453,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="230" spans="1:5" ht="30.75">
+    <row r="230" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A230" s="8">
         <v>228</v>
       </c>
@@ -7461,7 +7470,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="231" spans="1:5" ht="30.75">
+    <row r="231" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A231" s="8">
         <v>229</v>
       </c>
@@ -7478,7 +7487,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="232" spans="1:5" ht="30.75">
+    <row r="232" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A232" s="8">
         <v>230</v>
       </c>
@@ -7495,32 +7504,32 @@
         <v>582</v>
       </c>
     </row>
-    <row r="233" spans="1:5" ht="30.75">
-      <c r="A233" s="8">
+    <row r="233" spans="1:5" s="19" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A233" s="18">
         <v>231</v>
       </c>
-      <c r="B233" s="8" t="s">
+      <c r="B233" s="18" t="s">
         <v>591</v>
       </c>
-      <c r="C233" s="8" t="s">
+      <c r="C233" s="18" t="s">
         <v>592</v>
       </c>
-      <c r="D233" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E233" s="8" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="234" spans="1:5" ht="30.75">
+      <c r="D233" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="E233" s="18" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A234" s="8">
         <v>232</v>
       </c>
       <c r="B234" s="8" t="s">
+        <v>593</v>
+      </c>
+      <c r="C234" s="8" t="s">
         <v>594</v>
-      </c>
-      <c r="C234" s="8" t="s">
-        <v>595</v>
       </c>
       <c r="D234" s="8" t="s">
         <v>515</v>
@@ -7529,15 +7538,15 @@
         <v>582</v>
       </c>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A235" s="8">
         <v>233</v>
       </c>
       <c r="B235" s="8" t="s">
+        <v>595</v>
+      </c>
+      <c r="C235" s="8" t="s">
         <v>596</v>
-      </c>
-      <c r="C235" s="8" t="s">
-        <v>597</v>
       </c>
       <c r="D235" s="8" t="s">
         <v>515</v>
@@ -7546,2339 +7555,2339 @@
         <v>582</v>
       </c>
     </row>
-    <row r="236" spans="1:5" ht="30.75">
+    <row r="236" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A236" s="8">
         <v>234</v>
       </c>
       <c r="B236" s="8" t="s">
+        <v>597</v>
+      </c>
+      <c r="C236" s="8" t="s">
         <v>598</v>
       </c>
-      <c r="C236" s="8" t="s">
+      <c r="D236" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E236" s="8" t="s">
         <v>599</v>
       </c>
-      <c r="D236" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E236" s="8" t="s">
-        <v>600</v>
-      </c>
-    </row>
-    <row r="237" spans="1:5">
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A237" s="8">
         <v>235</v>
       </c>
       <c r="B237" s="8" t="s">
+        <v>600</v>
+      </c>
+      <c r="C237" s="8" t="s">
         <v>601</v>
       </c>
-      <c r="C237" s="8" t="s">
+      <c r="D237" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E237" s="8" t="s">
         <v>602</v>
       </c>
-      <c r="D237" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E237" s="8" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="238" spans="1:5" ht="30.75">
+    </row>
+    <row r="238" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A238" s="8">
         <v>236</v>
       </c>
       <c r="B238" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="C238" s="8" t="s">
         <v>604</v>
       </c>
-      <c r="C238" s="8" t="s">
+      <c r="D238" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E238" s="8" t="s">
         <v>605</v>
       </c>
-      <c r="D238" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E238" s="8" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="239" spans="1:5" ht="30.75">
+    </row>
+    <row r="239" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A239" s="8">
         <v>237</v>
       </c>
       <c r="B239" s="8" t="s">
+        <v>606</v>
+      </c>
+      <c r="C239" s="8" t="s">
         <v>607</v>
       </c>
-      <c r="C239" s="8" t="s">
-        <v>608</v>
-      </c>
       <c r="D239" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E239" s="8" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="240" spans="1:5" ht="30.75">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A240" s="8">
         <v>238</v>
       </c>
       <c r="B240" s="8" t="s">
+        <v>608</v>
+      </c>
+      <c r="C240" s="8" t="s">
         <v>609</v>
       </c>
-      <c r="C240" s="8" t="s">
-        <v>610</v>
-      </c>
       <c r="D240" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E240" s="8" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="241" spans="1:5" ht="30.75">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A241" s="8">
         <v>239</v>
       </c>
       <c r="B241" s="8" t="s">
+        <v>610</v>
+      </c>
+      <c r="C241" s="8" t="s">
         <v>611</v>
       </c>
-      <c r="C241" s="8" t="s">
+      <c r="D241" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E241" s="8" t="s">
         <v>612</v>
       </c>
-      <c r="D241" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E241" s="8" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="242" spans="1:5" ht="30.75">
+    </row>
+    <row r="242" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A242" s="8">
         <v>240</v>
       </c>
       <c r="B242" s="8" t="s">
+        <v>613</v>
+      </c>
+      <c r="C242" s="8" t="s">
         <v>614</v>
       </c>
-      <c r="C242" s="8" t="s">
-        <v>615</v>
-      </c>
       <c r="D242" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E242" s="8" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="243" spans="1:5" ht="30.75">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A243" s="8">
         <v>241</v>
       </c>
       <c r="B243" s="8" t="s">
+        <v>615</v>
+      </c>
+      <c r="C243" s="8" t="s">
         <v>616</v>
       </c>
-      <c r="C243" s="8" t="s">
+      <c r="D243" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E243" s="8" t="s">
         <v>617</v>
       </c>
-      <c r="D243" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E243" s="8" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="244" spans="1:5" ht="30.75">
+    </row>
+    <row r="244" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A244" s="8">
         <v>242</v>
       </c>
       <c r="B244" s="8" t="s">
+        <v>618</v>
+      </c>
+      <c r="C244" s="8" t="s">
         <v>619</v>
       </c>
-      <c r="C244" s="8" t="s">
-        <v>620</v>
-      </c>
       <c r="D244" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E244" s="8" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="245" spans="1:5">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A245" s="8">
         <v>243</v>
       </c>
       <c r="B245" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="C245" s="8" t="s">
         <v>621</v>
       </c>
-      <c r="C245" s="8" t="s">
-        <v>622</v>
-      </c>
       <c r="D245" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E245" s="8" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="246" spans="1:5" ht="30.75">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A246" s="8">
         <v>244</v>
       </c>
       <c r="B246" s="8" t="s">
+        <v>622</v>
+      </c>
+      <c r="C246" s="8" t="s">
         <v>623</v>
       </c>
-      <c r="C246" s="8" t="s">
-        <v>624</v>
-      </c>
       <c r="D246" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E246" s="8" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="247" spans="1:5" ht="30.75">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A247" s="8">
         <v>245</v>
       </c>
       <c r="B247" s="8" t="s">
+        <v>624</v>
+      </c>
+      <c r="C247" s="8" t="s">
         <v>625</v>
       </c>
-      <c r="C247" s="8" t="s">
+      <c r="D247" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E247" s="8" t="s">
         <v>626</v>
       </c>
-      <c r="D247" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E247" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="248" spans="1:5" ht="30.75">
+    </row>
+    <row r="248" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A248" s="8">
         <v>246</v>
       </c>
       <c r="B248" s="8" t="s">
+        <v>627</v>
+      </c>
+      <c r="C248" s="8" t="s">
         <v>628</v>
       </c>
-      <c r="C248" s="8" t="s">
+      <c r="D248" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E248" s="8" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" s="19" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A249" s="18">
+        <v>247</v>
+      </c>
+      <c r="B249" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="D248" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E248" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="249" spans="1:5" ht="30.75">
-      <c r="A249" s="8">
-        <v>247</v>
-      </c>
-      <c r="B249" s="8" t="s">
+      <c r="C249" s="18" t="s">
         <v>630</v>
       </c>
-      <c r="C249" s="8" t="s">
-        <v>631</v>
-      </c>
-      <c r="D249" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E249" s="8" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="250" spans="1:5" ht="30.75">
+      <c r="D249" s="18" t="s">
+        <v>515</v>
+      </c>
+      <c r="E249" s="18" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A250" s="8">
         <v>248</v>
       </c>
       <c r="B250" s="8" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C250" s="8" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D250" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E250" s="8" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="251" spans="1:5" ht="30.75">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A251" s="8">
         <v>249</v>
       </c>
       <c r="B251" s="8" t="s">
+        <v>633</v>
+      </c>
+      <c r="C251" s="8" t="s">
+        <v>634</v>
+      </c>
+      <c r="D251" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E251" s="8" t="s">
         <v>635</v>
       </c>
-      <c r="C251" s="8" t="s">
-        <v>636</v>
-      </c>
-      <c r="D251" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E251" s="8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="252" spans="1:5" ht="30.75">
+    </row>
+    <row r="252" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A252" s="8">
         <v>250</v>
       </c>
       <c r="B252" s="8" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C252" s="8" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D252" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E252" s="8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="253" spans="1:5" ht="30.75">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A253" s="8">
         <v>251</v>
       </c>
       <c r="B253" s="8" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C253" s="8" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D253" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E253" s="8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="254" spans="1:5" ht="45.75">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A254" s="8">
         <v>252</v>
       </c>
       <c r="B254" s="8" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C254" s="8" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D254" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E254" s="8" t="s">
-        <v>637</v>
-      </c>
-    </row>
-    <row r="255" spans="1:5" ht="30.75">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A255" s="8">
         <v>253</v>
       </c>
       <c r="B255" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="C255" s="8" t="s">
+        <v>643</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E255" s="8" t="s">
         <v>644</v>
       </c>
-      <c r="C255" s="8" t="s">
-        <v>645</v>
-      </c>
-      <c r="D255" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E255" s="8" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="256" spans="1:5" ht="30.75">
+    </row>
+    <row r="256" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A256" s="8">
         <v>254</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C256" s="8" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D256" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E256" s="8" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="257" spans="1:5" ht="30.75">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A257" s="8">
         <v>255</v>
       </c>
       <c r="B257" s="8" t="s">
+        <v>647</v>
+      </c>
+      <c r="C257" s="8" t="s">
+        <v>648</v>
+      </c>
+      <c r="D257" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E257" s="8" t="s">
         <v>649</v>
       </c>
-      <c r="C257" s="8" t="s">
-        <v>650</v>
-      </c>
-      <c r="D257" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E257" s="8" t="s">
-        <v>651</v>
-      </c>
-    </row>
-    <row r="258" spans="1:5" ht="30.75">
+    </row>
+    <row r="258" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A258" s="8">
         <v>256</v>
       </c>
       <c r="B258" s="8" t="s">
+        <v>650</v>
+      </c>
+      <c r="C258" s="8" t="s">
+        <v>651</v>
+      </c>
+      <c r="D258" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E258" s="8" t="s">
         <v>652</v>
       </c>
-      <c r="C258" s="8" t="s">
-        <v>653</v>
-      </c>
-      <c r="D258" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E258" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="259" spans="1:5" ht="30.75">
+    </row>
+    <row r="259" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A259" s="8">
         <v>257</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C259" s="8" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="D259" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E259" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="260" spans="1:5" ht="30.75">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A260" s="8">
         <v>258</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C260" s="8" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D260" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E260" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="261" spans="1:5" ht="30.75">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A261" s="8">
         <v>259</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C261" s="8" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="D261" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E261" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="262" spans="1:5" ht="30.75">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A262" s="8">
         <v>260</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C262" s="8" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="D262" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E262" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="263" spans="1:5" ht="30.75">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A263" s="8">
         <v>261</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C263" s="8" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="D263" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E263" s="8" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="264" spans="1:5" ht="30.75">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A264" s="8">
         <v>262</v>
       </c>
       <c r="B264" s="8" t="s">
+        <v>663</v>
+      </c>
+      <c r="C264" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="D264" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E264" s="8" t="s">
         <v>665</v>
       </c>
-      <c r="C264" s="8" t="s">
-        <v>666</v>
-      </c>
-      <c r="D264" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E264" s="8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="265" spans="1:5" ht="30.75">
+    </row>
+    <row r="265" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A265" s="8">
         <v>263</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="C265" s="8" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="D265" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E265" s="8" t="s">
-        <v>667</v>
-      </c>
-    </row>
-    <row r="266" spans="1:5" ht="30.75">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="8">
         <v>264</v>
       </c>
       <c r="B266" s="8" t="s">
+        <v>668</v>
+      </c>
+      <c r="C266" s="8" t="s">
+        <v>669</v>
+      </c>
+      <c r="D266" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E266" s="8" t="s">
         <v>670</v>
       </c>
-      <c r="C266" s="8" t="s">
-        <v>671</v>
-      </c>
-      <c r="D266" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E266" s="8" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="267" spans="1:5" ht="30.75">
+    </row>
+    <row r="267" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A267" s="8">
         <v>265</v>
       </c>
       <c r="B267" s="8" t="s">
+        <v>671</v>
+      </c>
+      <c r="C267" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="D267" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E267" s="8" t="s">
         <v>673</v>
       </c>
-      <c r="C267" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="D267" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E267" s="8" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="268" spans="1:5">
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A268" s="8">
         <v>266</v>
       </c>
       <c r="B268" s="8" t="s">
+        <v>674</v>
+      </c>
+      <c r="C268" s="8" t="s">
+        <v>675</v>
+      </c>
+      <c r="D268" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E268" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="C268" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="D268" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E268" s="10" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="269" spans="1:5">
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" s="8">
         <v>267</v>
       </c>
       <c r="B269" s="8" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C269" s="8" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D269" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E269" s="8" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="270" spans="1:5" ht="30.75">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A270" s="8">
         <v>268</v>
       </c>
       <c r="B270" s="8" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C270" s="8" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D270" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E270" s="8" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="271" spans="1:5" ht="30.75">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A271" s="8">
         <v>269</v>
       </c>
       <c r="B271" s="8" t="s">
+        <v>681</v>
+      </c>
+      <c r="C271" s="8" t="s">
+        <v>682</v>
+      </c>
+      <c r="D271" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E271" s="8" t="s">
         <v>683</v>
       </c>
-      <c r="C271" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="D271" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E271" s="8" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="272" spans="1:5" ht="30.75">
+    </row>
+    <row r="272" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A272" s="8">
         <v>270</v>
       </c>
       <c r="B272" s="8" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="C272" s="8" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="D272" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E272" s="8" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="273" spans="1:5" ht="30.75">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A273" s="8">
         <v>271</v>
       </c>
       <c r="B273" s="8" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C273" s="8" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="D273" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E273" s="8" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="274" spans="1:5">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A274" s="8">
         <v>272</v>
       </c>
       <c r="B274" s="8" t="s">
+        <v>688</v>
+      </c>
+      <c r="C274" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="D274" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E274" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="C274" s="8" t="s">
-        <v>691</v>
-      </c>
-      <c r="D274" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E274" s="8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="275" spans="1:5" ht="30.75">
+    </row>
+    <row r="275" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A275" s="8">
         <v>273</v>
       </c>
       <c r="B275" s="8" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C275" s="8" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D275" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E275" s="8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="276" spans="1:5" ht="30.75">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A276" s="8">
         <v>274</v>
       </c>
       <c r="B276" s="8" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C276" s="8" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="D276" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E276" s="8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="277" spans="1:5" ht="30.75">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A277" s="8">
         <v>275</v>
       </c>
       <c r="B277" s="8" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C277" s="8" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D277" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E277" s="8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="278" spans="1:5">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A278" s="8">
         <v>276</v>
       </c>
       <c r="B278" s="8" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C278" s="8" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="D278" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E278" s="8" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="279" spans="1:5" ht="30.75">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A279" s="8">
         <v>277</v>
       </c>
       <c r="B279" s="8" t="s">
+        <v>699</v>
+      </c>
+      <c r="C279" s="8" t="s">
+        <v>700</v>
+      </c>
+      <c r="D279" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E279" s="8" t="s">
         <v>701</v>
       </c>
-      <c r="C279" s="8" t="s">
-        <v>702</v>
-      </c>
-      <c r="D279" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E279" s="8" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="280" spans="1:5" ht="30.75">
+    </row>
+    <row r="280" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A280" s="8">
         <v>278</v>
       </c>
       <c r="B280" s="8" t="s">
+        <v>702</v>
+      </c>
+      <c r="C280" s="8" t="s">
+        <v>703</v>
+      </c>
+      <c r="D280" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E280" s="8" t="s">
         <v>704</v>
       </c>
-      <c r="C280" s="8" t="s">
+    </row>
+    <row r="281" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+      <c r="A281" s="8">
+        <v>279</v>
+      </c>
+      <c r="B281" s="8" t="s">
         <v>705</v>
       </c>
-      <c r="D280" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E280" s="8" t="s">
+      <c r="C281" s="8" t="s">
         <v>706</v>
       </c>
-    </row>
-    <row r="281" spans="1:5" ht="30.75">
-      <c r="A281" s="8">
-        <v>279</v>
-      </c>
-      <c r="B281" s="8" t="s">
-        <v>707</v>
-      </c>
-      <c r="C281" s="8" t="s">
-        <v>708</v>
-      </c>
       <c r="D281" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E281" s="8" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="282" spans="1:5" ht="30.75">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A282" s="8">
         <v>280</v>
       </c>
       <c r="B282" s="8" t="s">
+        <v>707</v>
+      </c>
+      <c r="C282" s="8" t="s">
+        <v>708</v>
+      </c>
+      <c r="D282" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E282" s="8" t="s">
         <v>709</v>
       </c>
-      <c r="C282" s="8" t="s">
-        <v>710</v>
-      </c>
-      <c r="D282" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E282" s="8" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="283" spans="1:5" ht="30.75">
+    </row>
+    <row r="283" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A283" s="8">
         <v>281</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="C283" s="8" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D283" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E283" s="8" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="284" spans="1:5" ht="30.75">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A284" s="8">
         <v>282</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C284" s="8" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D284" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E284" s="8" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="285" spans="1:5" ht="30.75">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A285" s="8">
         <v>283</v>
       </c>
       <c r="B285" s="8" t="s">
+        <v>714</v>
+      </c>
+      <c r="C285" s="8" t="s">
+        <v>715</v>
+      </c>
+      <c r="D285" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E285" s="8" t="s">
         <v>716</v>
       </c>
-      <c r="C285" s="8" t="s">
-        <v>717</v>
-      </c>
-      <c r="D285" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E285" s="8" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="286" spans="1:5" ht="30.75">
+    </row>
+    <row r="286" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A286" s="8">
         <v>284</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C286" s="8" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D286" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E286" s="8" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="287" spans="1:5" ht="30.75">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A287" s="8">
         <v>285</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C287" s="8" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D287" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E287" s="8" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="288" spans="1:5" ht="30.75">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A288" s="8">
         <v>286</v>
       </c>
       <c r="B288" s="8" t="s">
+        <v>721</v>
+      </c>
+      <c r="C288" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="D288" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E288" s="8" t="s">
         <v>723</v>
       </c>
-      <c r="C288" s="8" t="s">
-        <v>724</v>
-      </c>
-      <c r="D288" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E288" s="8" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="289" spans="1:5" ht="30.75">
+    </row>
+    <row r="289" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A289" s="8">
         <v>287</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C289" s="8" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="D289" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E289" s="8" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" ht="30.75">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A290" s="8">
         <v>288</v>
       </c>
       <c r="B290" s="8" t="s">
+        <v>726</v>
+      </c>
+      <c r="C290" s="8" t="s">
+        <v>727</v>
+      </c>
+      <c r="D290" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E290" s="8" t="s">
         <v>728</v>
       </c>
-      <c r="C290" s="8" t="s">
-        <v>729</v>
-      </c>
-      <c r="D290" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E290" s="8" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" ht="30.75">
+    </row>
+    <row r="291" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A291" s="8">
         <v>289</v>
       </c>
       <c r="B291" s="8" t="s">
+        <v>729</v>
+      </c>
+      <c r="C291" s="8" t="s">
+        <v>730</v>
+      </c>
+      <c r="D291" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E291" s="8" t="s">
         <v>731</v>
       </c>
-      <c r="C291" s="8" t="s">
-        <v>732</v>
-      </c>
-      <c r="D291" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E291" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="292" spans="1:5">
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A292" s="8">
         <v>290</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C292" s="8" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="D292" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E292" s="8" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="293" spans="1:5" ht="30.75">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A293" s="8">
         <v>291</v>
       </c>
       <c r="B293" s="8" t="s">
+        <v>734</v>
+      </c>
+      <c r="C293" s="8" t="s">
+        <v>735</v>
+      </c>
+      <c r="D293" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E293" s="8" t="s">
         <v>736</v>
       </c>
-      <c r="C293" s="8" t="s">
-        <v>737</v>
-      </c>
-      <c r="D293" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E293" s="8" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="294" spans="1:5" ht="30.75">
+    </row>
+    <row r="294" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A294" s="8">
         <v>292</v>
       </c>
       <c r="B294" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="C294" s="8" t="s">
+        <v>738</v>
+      </c>
+      <c r="D294" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E294" s="8" t="s">
         <v>739</v>
       </c>
-      <c r="C294" s="8" t="s">
-        <v>740</v>
-      </c>
-      <c r="D294" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E294" s="8" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="295" spans="1:5" ht="30.75">
+    </row>
+    <row r="295" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A295" s="8">
         <v>293</v>
       </c>
       <c r="B295" s="8" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C295" s="8" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="D295" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E295" s="8" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="296" spans="1:5" ht="30.75">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A296" s="8">
         <v>294</v>
       </c>
       <c r="B296" s="8" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="C296" s="8" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D296" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E296" s="8" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="297" spans="1:5">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A297" s="8">
         <v>295</v>
       </c>
       <c r="B297" s="8" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="C297" s="8" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D297" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E297" s="8" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="298" spans="1:5" ht="30.75">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A298" s="8">
         <v>296</v>
       </c>
       <c r="B298" s="8" t="s">
+        <v>746</v>
+      </c>
+      <c r="C298" s="8" t="s">
+        <v>747</v>
+      </c>
+      <c r="D298" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E298" s="8" t="s">
         <v>748</v>
       </c>
-      <c r="C298" s="8" t="s">
-        <v>749</v>
-      </c>
-      <c r="D298" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E298" s="8" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="299" spans="1:5">
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A299" s="8">
         <v>297</v>
       </c>
       <c r="B299" s="8" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C299" s="8" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D299" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E299" s="8" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="300" spans="1:5" ht="30.75">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A300" s="8">
         <v>298</v>
       </c>
       <c r="B300" s="8" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C300" s="8" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D300" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E300" s="8" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="301" spans="1:5" ht="30.75">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A301" s="8">
         <v>299</v>
       </c>
       <c r="B301" s="8" t="s">
+        <v>753</v>
+      </c>
+      <c r="C301" s="8" t="s">
+        <v>754</v>
+      </c>
+      <c r="D301" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E301" s="8" t="s">
         <v>755</v>
       </c>
-      <c r="C301" s="8" t="s">
-        <v>756</v>
-      </c>
-      <c r="D301" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E301" s="8" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="302" spans="1:5">
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A302" s="8">
         <v>300</v>
       </c>
       <c r="B302" s="8" t="s">
+        <v>756</v>
+      </c>
+      <c r="C302" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="D302" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E302" s="8" t="s">
         <v>758</v>
       </c>
-      <c r="C302" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="D302" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E302" s="8" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="303" spans="1:5">
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A303" s="6">
         <v>301</v>
       </c>
       <c r="B303" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="C303" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="D303" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E303" s="4" t="s">
         <v>761</v>
       </c>
-      <c r="C303" s="4" t="s">
-        <v>762</v>
-      </c>
-      <c r="D303" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E303" s="4" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="304" spans="1:5" ht="45.75">
+    </row>
+    <row r="304" spans="1:5" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A304" s="7">
         <v>302</v>
       </c>
       <c r="B304" s="5" t="s">
+        <v>762</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="D304" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E304" s="4" t="s">
         <v>764</v>
       </c>
-      <c r="C304" s="5" t="s">
-        <v>765</v>
-      </c>
-      <c r="D304" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E304" s="4" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="305" spans="1:5" ht="30.75">
+    </row>
+    <row r="305" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A305" s="7">
         <v>303</v>
       </c>
       <c r="B305" s="5" t="s">
+        <v>765</v>
+      </c>
+      <c r="C305" s="8" t="s">
+        <v>766</v>
+      </c>
+      <c r="D305" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E305" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="C305" s="8" t="s">
-        <v>768</v>
-      </c>
-      <c r="D305" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E305" s="4" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="306" spans="1:5" ht="30.75">
+    </row>
+    <row r="306" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A306" s="7">
         <v>304</v>
       </c>
       <c r="B306" s="5" t="s">
+        <v>768</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>769</v>
+      </c>
+      <c r="D306" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E306" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C306" s="5" t="s">
-        <v>771</v>
-      </c>
-      <c r="D306" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E306" s="4" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="307" spans="1:5" ht="30.75">
+    </row>
+    <row r="307" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A307" s="7">
         <v>305</v>
       </c>
       <c r="B307" s="5" t="s">
+        <v>771</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>772</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E307" s="4" t="s">
         <v>773</v>
       </c>
-      <c r="C307" s="5" t="s">
-        <v>774</v>
-      </c>
-      <c r="D307" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E307" s="4" t="s">
-        <v>775</v>
-      </c>
-    </row>
-    <row r="308" spans="1:5">
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A308" s="7">
         <v>306</v>
       </c>
       <c r="B308" s="5" t="s">
+        <v>774</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E308" s="4" t="s">
         <v>776</v>
       </c>
-      <c r="C308" s="5" t="s">
-        <v>777</v>
-      </c>
-      <c r="D308" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E308" s="4" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="309" spans="1:5">
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A309" s="7">
         <v>307</v>
       </c>
       <c r="B309" s="5" t="s">
+        <v>777</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>778</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E309" s="5" t="s">
         <v>779</v>
       </c>
-      <c r="C309" s="5" t="s">
-        <v>780</v>
-      </c>
-      <c r="D309" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E309" s="5" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="310" spans="1:5">
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A310" s="7">
         <v>308</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>7</v>
       </c>
       <c r="E310" s="5" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="311" spans="1:5">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A311" s="7">
         <v>309</v>
       </c>
       <c r="B311" s="5" t="s">
+        <v>782</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>783</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E311" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="C311" s="5" t="s">
-        <v>785</v>
-      </c>
-      <c r="D311" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E311" s="5" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="312" spans="1:5">
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A312" s="7">
         <v>310</v>
       </c>
       <c r="B312" s="5" t="s">
+        <v>785</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>786</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E312" s="5" t="s">
         <v>787</v>
       </c>
-      <c r="C312" s="5" t="s">
-        <v>788</v>
-      </c>
-      <c r="D312" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E312" s="5" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="313" spans="1:5" ht="30.75">
+    </row>
+    <row r="313" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A313" s="7">
         <v>311</v>
       </c>
       <c r="B313" s="5" t="s">
+        <v>788</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>789</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E313" s="5" t="s">
         <v>790</v>
       </c>
-      <c r="C313" s="5" t="s">
-        <v>791</v>
-      </c>
-      <c r="D313" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E313" s="5" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="314" spans="1:5">
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A314" s="7">
         <v>312</v>
       </c>
       <c r="B314" s="5" t="s">
+        <v>791</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>792</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E314" s="5" t="s">
         <v>793</v>
       </c>
-      <c r="C314" s="5" t="s">
-        <v>794</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E314" s="5" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="315" spans="1:5" ht="30.75">
+    </row>
+    <row r="315" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A315" s="7">
         <v>313</v>
       </c>
       <c r="B315" s="5" t="s">
+        <v>794</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E315" s="5" t="s">
         <v>796</v>
       </c>
-      <c r="C315" s="5" t="s">
-        <v>797</v>
-      </c>
-      <c r="D315" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E315" s="5" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="316" spans="1:5" ht="30.75">
+    </row>
+    <row r="316" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A316" s="7">
         <v>314</v>
       </c>
       <c r="B316" s="5" t="s">
+        <v>797</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>798</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E316" s="5" t="s">
         <v>799</v>
       </c>
-      <c r="C316" s="5" t="s">
-        <v>800</v>
-      </c>
-      <c r="D316" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E316" s="5" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="317" spans="1:5">
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A317" s="7">
         <v>315</v>
       </c>
       <c r="B317" s="5" t="s">
+        <v>800</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>801</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E317" s="5" t="s">
         <v>802</v>
       </c>
-      <c r="C317" s="5" t="s">
-        <v>803</v>
-      </c>
-      <c r="D317" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E317" s="5" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="318" spans="1:5">
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A318" s="6">
         <v>316</v>
       </c>
       <c r="B318" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E318" s="5" t="s">
         <v>805</v>
       </c>
-      <c r="C318" s="4" t="s">
-        <v>806</v>
-      </c>
-      <c r="D318" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E318" s="5" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="319" spans="1:5" ht="30.75">
+    </row>
+    <row r="319" spans="1:5" ht="29" x14ac:dyDescent="0.35">
       <c r="A319" s="7">
         <v>317</v>
       </c>
       <c r="B319" s="5" t="s">
+        <v>806</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>807</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E319" s="5" t="s">
         <v>808</v>
       </c>
-      <c r="C319" s="5" t="s">
-        <v>809</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E319" s="5" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="320" spans="1:5">
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A320" s="7">
         <v>318</v>
       </c>
       <c r="B320" s="5" t="s">
+        <v>809</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E320" s="5" t="s">
         <v>811</v>
       </c>
-      <c r="C320" s="5" t="s">
-        <v>812</v>
-      </c>
-      <c r="D320" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E320" s="5" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="321" spans="1:5">
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A321" s="7">
         <v>319</v>
       </c>
       <c r="B321" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E321" s="5" t="s">
         <v>814</v>
       </c>
-      <c r="C321" s="5" t="s">
-        <v>815</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E321" s="5" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="322" spans="1:5">
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A322" s="7">
         <v>320</v>
       </c>
       <c r="B322" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E322" s="5" t="s">
         <v>817</v>
       </c>
-      <c r="C322" s="5" t="s">
-        <v>818</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E322" s="5" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="323" spans="1:5">
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A323" s="14">
         <v>321</v>
       </c>
       <c r="B323" s="12" t="s">
+        <v>818</v>
+      </c>
+      <c r="C323" s="12" t="s">
+        <v>819</v>
+      </c>
+      <c r="D323" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E323" s="12" t="s">
         <v>820</v>
       </c>
-      <c r="C323" s="12" t="s">
-        <v>821</v>
-      </c>
-      <c r="D323" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E323" s="12" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="324" spans="1:5">
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A324" s="14">
         <v>322</v>
       </c>
       <c r="B324" s="12" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C324" s="12" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D324" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E324" s="12" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="325" spans="1:5">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A325" s="14">
         <v>323</v>
       </c>
       <c r="B325" s="12" t="s">
+        <v>823</v>
+      </c>
+      <c r="C325" s="12" t="s">
+        <v>824</v>
+      </c>
+      <c r="D325" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E325" s="12" t="s">
         <v>825</v>
       </c>
-      <c r="C325" s="12" t="s">
-        <v>826</v>
-      </c>
-      <c r="D325" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E325" s="12" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="326" spans="1:5">
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A326" s="14">
         <v>324</v>
       </c>
       <c r="B326" s="12" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="C326" s="12" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D326" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E326" s="12" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="327" spans="1:5">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A327" s="14">
         <v>325</v>
       </c>
       <c r="B327" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="C327" s="12" t="s">
+        <v>829</v>
+      </c>
+      <c r="D327" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E327" s="12" t="s">
         <v>830</v>
       </c>
-      <c r="C327" s="12" t="s">
-        <v>831</v>
-      </c>
-      <c r="D327" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E327" s="12" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="328" spans="1:5">
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A328" s="14">
         <v>326</v>
       </c>
       <c r="B328" s="12" t="s">
+        <v>831</v>
+      </c>
+      <c r="C328" s="12" t="s">
+        <v>832</v>
+      </c>
+      <c r="D328" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E328" s="12" t="s">
         <v>833</v>
       </c>
-      <c r="C328" s="12" t="s">
-        <v>834</v>
-      </c>
-      <c r="D328" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E328" s="12" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="329" spans="1:5">
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A329" s="14">
         <v>327</v>
       </c>
       <c r="B329" s="12" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C329" s="12" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D329" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E329" s="12" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="330" spans="1:5">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A330" s="14">
         <v>328</v>
       </c>
       <c r="B330" s="12" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C330" s="12" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D330" s="12" t="s">
         <v>279</v>
       </c>
       <c r="E330" s="12" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="331" spans="1:5">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A331" s="14">
         <v>329</v>
       </c>
       <c r="B331" s="12" t="s">
+        <v>838</v>
+      </c>
+      <c r="C331" s="12" t="s">
+        <v>839</v>
+      </c>
+      <c r="D331" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E331" s="12" t="s">
         <v>840</v>
       </c>
-      <c r="C331" s="12" t="s">
-        <v>841</v>
-      </c>
-      <c r="D331" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="E331" s="12" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="332" spans="1:5">
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A332" s="15">
         <v>330</v>
       </c>
       <c r="B332" s="15" t="s">
+        <v>841</v>
+      </c>
+      <c r="C332" s="15" t="s">
+        <v>842</v>
+      </c>
+      <c r="D332" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E332" s="15" t="s">
         <v>843</v>
       </c>
-      <c r="C332" s="15" t="s">
-        <v>844</v>
-      </c>
-      <c r="D332" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E332" s="15" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="333" spans="1:5">
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A333" s="15">
         <v>331</v>
       </c>
       <c r="B333" s="15" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="C333" s="15" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="D333" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E333" s="15" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="334" spans="1:5">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A334" s="15">
         <v>332</v>
       </c>
       <c r="B334" s="15" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="C334" s="15" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="D334" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E334" s="15" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="335" spans="1:5">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A335" s="15">
         <v>333</v>
       </c>
       <c r="B335" s="15" t="s">
+        <v>848</v>
+      </c>
+      <c r="C335" s="15" t="s">
+        <v>849</v>
+      </c>
+      <c r="D335" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E335" s="15" t="s">
         <v>850</v>
       </c>
-      <c r="C335" s="15" t="s">
-        <v>851</v>
-      </c>
-      <c r="D335" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E335" s="15" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="336" spans="1:5">
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A336" s="15">
         <v>334</v>
       </c>
       <c r="B336" s="15" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C336" s="15" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D336" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E336" s="15" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="337" spans="1:5">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A337" s="15">
         <v>335</v>
       </c>
       <c r="B337" s="15" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="C337" s="15" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="D337" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E337" s="15" t="s">
-        <v>852</v>
-      </c>
-    </row>
-    <row r="338" spans="1:5">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A338" s="15">
         <v>336</v>
       </c>
       <c r="B338" s="15" t="s">
+        <v>855</v>
+      </c>
+      <c r="C338" s="15" t="s">
+        <v>856</v>
+      </c>
+      <c r="D338" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E338" s="15" t="s">
         <v>857</v>
       </c>
-      <c r="C338" s="15" t="s">
-        <v>858</v>
-      </c>
-      <c r="D338" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E338" s="15" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="339" spans="1:5">
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A339" s="15">
         <v>337</v>
       </c>
       <c r="B339" s="15" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C339" s="15" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D339" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E339" s="15" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="340" spans="1:5">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A340" s="15">
         <v>338</v>
       </c>
       <c r="B340" s="15" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="C340" s="15" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="D340" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E340" s="15" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="341" spans="1:5">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A341" s="15">
         <v>339</v>
       </c>
       <c r="B341" s="15" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="C341" s="15" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="D341" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E341" s="15" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="342" spans="1:5">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A342" s="15">
         <v>340</v>
       </c>
       <c r="B342" s="15" t="s">
+        <v>864</v>
+      </c>
+      <c r="C342" s="15" t="s">
+        <v>865</v>
+      </c>
+      <c r="D342" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E342" s="15" t="s">
         <v>866</v>
       </c>
-      <c r="C342" s="15" t="s">
-        <v>867</v>
-      </c>
-      <c r="D342" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E342" s="15" t="s">
-        <v>868</v>
-      </c>
-    </row>
-    <row r="343" spans="1:5">
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A343" s="15">
         <v>341</v>
       </c>
       <c r="B343" s="15" t="s">
+        <v>867</v>
+      </c>
+      <c r="C343" s="15" t="s">
+        <v>868</v>
+      </c>
+      <c r="D343" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E343" s="15" t="s">
         <v>869</v>
       </c>
-      <c r="C343" s="15" t="s">
-        <v>870</v>
-      </c>
-      <c r="D343" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E343" s="15" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="344" spans="1:5">
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A344" s="15">
         <v>342</v>
       </c>
       <c r="B344" s="15" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="C344" s="15" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="D344" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E344" s="15" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="345" spans="1:5">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A345" s="15">
         <v>343</v>
       </c>
       <c r="B345" s="15" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C345" s="15" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="D345" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E345" s="15" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="346" spans="1:5">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A346" s="15">
         <v>344</v>
       </c>
       <c r="B346" s="15" t="s">
+        <v>874</v>
+      </c>
+      <c r="C346" s="15" t="s">
+        <v>875</v>
+      </c>
+      <c r="D346" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E346" s="15" t="s">
         <v>876</v>
       </c>
-      <c r="C346" s="15" t="s">
-        <v>877</v>
-      </c>
-      <c r="D346" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E346" s="15" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="347" spans="1:5">
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A347" s="15">
         <v>345</v>
       </c>
       <c r="B347" s="15" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C347" s="15" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D347" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E347" s="15" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="348" spans="1:5">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A348" s="15">
         <v>346</v>
       </c>
       <c r="B348" s="15" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="C348" s="15" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="D348" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E348" s="15" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="349" spans="1:5">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A349" s="15">
         <v>347</v>
       </c>
       <c r="B349" s="15" t="s">
+        <v>881</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>882</v>
+      </c>
+      <c r="D349" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E349" s="15" t="s">
         <v>883</v>
       </c>
-      <c r="C349" s="15" t="s">
-        <v>884</v>
-      </c>
-      <c r="D349" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E349" s="15" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="350" spans="1:5">
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A350" s="15">
         <v>348</v>
       </c>
       <c r="B350" s="15" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="C350" s="15" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="D350" s="15" t="s">
         <v>279</v>
       </c>
       <c r="E350" s="15" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="351" spans="1:5">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A351" s="15">
         <v>349</v>
       </c>
       <c r="B351" s="15" t="s">
+        <v>886</v>
+      </c>
+      <c r="C351" s="15" t="s">
+        <v>887</v>
+      </c>
+      <c r="D351" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E351" s="15" t="s">
         <v>888</v>
       </c>
-      <c r="C351" s="15" t="s">
-        <v>889</v>
-      </c>
-      <c r="D351" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E351" s="15" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="352" spans="1:5">
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A352" s="15">
         <v>350</v>
       </c>
       <c r="B352" s="15" t="s">
+        <v>889</v>
+      </c>
+      <c r="C352" s="15" t="s">
+        <v>890</v>
+      </c>
+      <c r="D352" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E352" s="15" t="s">
         <v>891</v>
       </c>
-      <c r="C352" s="15" t="s">
-        <v>892</v>
-      </c>
-      <c r="D352" s="15" t="s">
-        <v>279</v>
-      </c>
-      <c r="E352" s="15" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="353" spans="1:5">
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A353" s="15">
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="C353" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="D353" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E353" s="8" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="354" spans="1:5">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A354" s="15">
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="C354" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="D354" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E354" s="8" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="355" spans="1:5">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A355" s="15">
         <v>353</v>
       </c>
       <c r="B355" t="s">
+        <v>896</v>
+      </c>
+      <c r="C355" t="s">
+        <v>897</v>
+      </c>
+      <c r="D355" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E355" s="8" t="s">
         <v>898</v>
       </c>
-      <c r="C355" t="s">
-        <v>899</v>
-      </c>
-      <c r="D355" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E355" s="8" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="356" spans="1:5">
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A356" s="15">
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="C356" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="D356" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E356" s="8" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="357" spans="1:5">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A357" s="15">
         <v>355</v>
       </c>
       <c r="B357" t="s">
+        <v>901</v>
+      </c>
+      <c r="C357" t="s">
+        <v>902</v>
+      </c>
+      <c r="D357" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E357" s="8" t="s">
         <v>903</v>
       </c>
-      <c r="C357" t="s">
-        <v>904</v>
-      </c>
-      <c r="D357" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E357" s="8" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="358" spans="1:5">
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A358" s="15">
         <v>356</v>
       </c>
       <c r="B358" t="s">
+        <v>904</v>
+      </c>
+      <c r="C358" t="s">
+        <v>905</v>
+      </c>
+      <c r="D358" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E358" s="8" t="s">
         <v>906</v>
       </c>
-      <c r="C358" t="s">
-        <v>907</v>
-      </c>
-      <c r="D358" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E358" s="8" t="s">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="359" spans="1:5">
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A359" s="15">
         <v>357</v>
       </c>
       <c r="B359" t="s">
+        <v>907</v>
+      </c>
+      <c r="C359" t="s">
+        <v>908</v>
+      </c>
+      <c r="D359" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E359" s="8" t="s">
         <v>909</v>
       </c>
-      <c r="C359" t="s">
-        <v>910</v>
-      </c>
-      <c r="D359" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E359" s="8" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="360" spans="1:5">
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A360" s="15">
         <v>358</v>
       </c>
       <c r="B360" t="s">
+        <v>910</v>
+      </c>
+      <c r="C360" t="s">
+        <v>911</v>
+      </c>
+      <c r="D360" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E360" s="8" t="s">
         <v>912</v>
       </c>
-      <c r="C360" t="s">
-        <v>913</v>
-      </c>
-      <c r="D360" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E360" s="8" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="361" spans="1:5">
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A361" s="15">
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
       <c r="C361" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
       <c r="D361" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E361" s="8" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="362" spans="1:5">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A362" s="15">
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
       <c r="C362" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="D362" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E362" s="8" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="363" spans="1:5">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A363" s="15">
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="C363" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="D363" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E363" s="8" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="364" spans="1:5">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A364" s="15">
         <v>362</v>
       </c>
       <c r="B364" t="s">
+        <v>919</v>
+      </c>
+      <c r="C364" t="s">
+        <v>920</v>
+      </c>
+      <c r="D364" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E364" s="8" t="s">
         <v>921</v>
       </c>
-      <c r="C364" t="s">
-        <v>922</v>
-      </c>
-      <c r="D364" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E364" s="8" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="365" spans="1:5">
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A365" s="15">
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
       <c r="C365" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
       <c r="D365" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E365" s="8" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="366" spans="1:5">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A366" s="15">
         <v>364</v>
       </c>
       <c r="B366" t="s">
+        <v>924</v>
+      </c>
+      <c r="C366" t="s">
+        <v>925</v>
+      </c>
+      <c r="D366" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E366" s="8" t="s">
         <v>926</v>
       </c>
-      <c r="C366" t="s">
-        <v>927</v>
-      </c>
-      <c r="D366" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E366" s="8" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="367" spans="1:5">
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A367" s="15">
         <v>365</v>
       </c>
       <c r="B367" t="s">
+        <v>927</v>
+      </c>
+      <c r="C367" t="s">
+        <v>928</v>
+      </c>
+      <c r="D367" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E367" s="8" t="s">
         <v>929</v>
       </c>
-      <c r="C367" t="s">
-        <v>930</v>
-      </c>
-      <c r="D367" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E367" s="8" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="368" spans="1:5">
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A368" s="15">
         <v>366</v>
       </c>
       <c r="B368" t="s">
+        <v>930</v>
+      </c>
+      <c r="C368" t="s">
+        <v>931</v>
+      </c>
+      <c r="D368" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E368" s="8" t="s">
         <v>932</v>
       </c>
-      <c r="C368" t="s">
-        <v>933</v>
-      </c>
-      <c r="D368" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E368" s="8" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="369" spans="1:5">
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A369" s="15">
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
       <c r="C369" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
       <c r="D369" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E369" s="8" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="370" spans="1:5">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A370" s="15">
         <v>368</v>
       </c>
       <c r="B370" t="s">
+        <v>935</v>
+      </c>
+      <c r="C370" t="s">
+        <v>936</v>
+      </c>
+      <c r="D370" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E370" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="C370" t="s">
-        <v>938</v>
-      </c>
-      <c r="D370" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E370" s="8" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="371" spans="1:5">
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A371" s="15">
         <v>369</v>
       </c>
       <c r="B371" t="s">
+        <v>938</v>
+      </c>
+      <c r="C371" t="s">
+        <v>939</v>
+      </c>
+      <c r="D371" s="8" t="s">
+        <v>515</v>
+      </c>
+      <c r="E371" s="8" t="s">
         <v>940</v>
       </c>
-      <c r="C371" t="s">
-        <v>941</v>
-      </c>
-      <c r="D371" s="8" t="s">
-        <v>515</v>
-      </c>
-      <c r="E371" s="8" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="372" spans="1:5">
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A372" s="15">
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
       <c r="C372" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
       <c r="D372" s="8" t="s">
         <v>515</v>
       </c>
       <c r="E372" s="8" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="373" spans="1:5">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D373" s="8"/>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.35">
       <c r="D374" s="8"/>
     </row>
   </sheetData>
